--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.01491230120872</v>
+        <v>11.86492324894642</v>
       </c>
       <c r="D2" t="n">
-        <v>75.00626358745272</v>
+        <v>12.18851783296107</v>
       </c>
       <c r="E2" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F2" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>99.25528159003494</v>
+        <v>16.12898325838068</v>
       </c>
       <c r="D3" t="n">
-        <v>100.5208059336734</v>
+        <v>16.33463096422193</v>
       </c>
       <c r="E3" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F3" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.58195949995852</v>
+        <v>10.33206841874326</v>
       </c>
       <c r="D4" t="n">
-        <v>65.54152754470219</v>
+        <v>10.65049822601411</v>
       </c>
       <c r="E4" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F4" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.22849061605341</v>
+        <v>9.624629725108679</v>
       </c>
       <c r="D5" t="n">
-        <v>61.20323585185713</v>
+        <v>9.945525825926785</v>
       </c>
       <c r="E5" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F5" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.73905541909456</v>
+        <v>9.220096505602866</v>
       </c>
       <c r="D6" t="n">
-        <v>58.68636758555267</v>
+        <v>9.536534732652308</v>
       </c>
       <c r="E6" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F6" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.3320439258492</v>
+        <v>9.641457137950495</v>
       </c>
       <c r="D7" t="n">
-        <v>61.13030234047375</v>
+        <v>9.933674130326985</v>
       </c>
       <c r="E7" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F7" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.1517589416072</v>
+        <v>8.14966082801117</v>
       </c>
       <c r="D8" t="n">
-        <v>52.0288231051622</v>
+        <v>8.454683754588858</v>
       </c>
       <c r="E8" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F8" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>91.02387605354622</v>
+        <v>14.79137985870126</v>
       </c>
       <c r="D9" t="n">
-        <v>92.08084862230294</v>
+        <v>14.96313790112423</v>
       </c>
       <c r="E9" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F9" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.823742157087</v>
+        <v>7.771358100526637</v>
       </c>
       <c r="D10" t="n">
-        <v>49.80413869621759</v>
+        <v>8.093172538135359</v>
       </c>
       <c r="E10" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F10" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.3304217532157</v>
+        <v>9.966193534897553</v>
       </c>
       <c r="D11" t="n">
-        <v>62.73989583720318</v>
+        <v>10.19523307354552</v>
       </c>
       <c r="E11" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F11" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>65.90606669960266</v>
+        <v>10.70973583868543</v>
       </c>
       <c r="D12" t="n">
-        <v>67.06035354507426</v>
+        <v>10.89730745107457</v>
       </c>
       <c r="E12" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F12" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.53611796109485</v>
+        <v>7.887119168677913</v>
       </c>
       <c r="D13" t="n">
-        <v>49.96366586728146</v>
+        <v>8.119095703433238</v>
       </c>
       <c r="E13" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F13" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.9219574116411</v>
+        <v>7.299818079391679</v>
       </c>
       <c r="D14" t="n">
-        <v>46.07016917983251</v>
+        <v>7.486402491722783</v>
       </c>
       <c r="E14" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F14" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.42697899055493</v>
+        <v>3.644384085965176</v>
       </c>
       <c r="D15" t="n">
-        <v>24.37148046951908</v>
+        <v>3.96036557629685</v>
       </c>
       <c r="E15" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F15" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>41.51231532518478</v>
+        <v>6.745751240342527</v>
       </c>
       <c r="D16" t="n">
-        <v>43.29504749629887</v>
+        <v>7.035445218148567</v>
       </c>
       <c r="E16" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F16" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.62720592735138</v>
+        <v>6.439420963194599</v>
       </c>
       <c r="D17" t="n">
-        <v>40.37084580873336</v>
+        <v>6.560262443919171</v>
       </c>
       <c r="E17" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F17" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>19.48865453932311</v>
+        <v>3.166906362640006</v>
       </c>
       <c r="D18" t="n">
-        <v>20.48692377696845</v>
+        <v>3.329125113757373</v>
       </c>
       <c r="E18" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F18" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.72447719039949</v>
+        <v>6.292727543439917</v>
       </c>
       <c r="D19" t="n">
-        <v>39.15812576129695</v>
+        <v>6.363195436210755</v>
       </c>
       <c r="E19" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F19" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>28.84125461795556</v>
+        <v>4.686703875417779</v>
       </c>
       <c r="D20" t="n">
-        <v>30.27279821718233</v>
+        <v>4.919329710292129</v>
       </c>
       <c r="E20" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F20" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>12.40326242502185</v>
+        <v>2.015530144066051</v>
       </c>
       <c r="D21" t="n">
-        <v>13.31916792544655</v>
+        <v>2.164364787885064</v>
       </c>
       <c r="E21" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F21" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>9.451051363019575</v>
+        <v>1.535795846490681</v>
       </c>
       <c r="D22" t="n">
-        <v>10.00321765567485</v>
+        <v>1.625522869047162</v>
       </c>
       <c r="E22" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F22" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>18.41829400284022</v>
+        <v>2.992972775461536</v>
       </c>
       <c r="D23" t="n">
-        <v>18.76668698318257</v>
+        <v>3.049586634767167</v>
       </c>
       <c r="E23" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F23" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>40.90709762348325</v>
+        <v>6.647403363816029</v>
       </c>
       <c r="D24" t="n">
-        <v>41.0114621760782</v>
+        <v>6.664362603612709</v>
       </c>
       <c r="E24" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F24" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>5.151180349651256</v>
+        <v>0.8370668068183292</v>
       </c>
       <c r="D25" t="n">
-        <v>3.196601643466112</v>
+        <v>0.5194477670632431</v>
       </c>
       <c r="E25" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F25" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>15.42081412792105</v>
+        <v>2.505882295787171</v>
       </c>
       <c r="D26" t="n">
-        <v>14.8232222566154</v>
+        <v>2.408773616700002</v>
       </c>
       <c r="E26" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F26" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>22.16369315173253</v>
+        <v>3.601600137156537</v>
       </c>
       <c r="D27" t="n">
-        <v>20.42799540500868</v>
+        <v>3.319549253313911</v>
       </c>
       <c r="E27" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F27" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>31.06535615257665</v>
+        <v>5.048120374793706</v>
       </c>
       <c r="D28" t="n">
-        <v>30.27650336536049</v>
+        <v>4.919931796871079</v>
       </c>
       <c r="E28" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F28" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>31.99805095650631</v>
+        <v>5.199683280432276</v>
       </c>
       <c r="D29" t="n">
-        <v>30.30736634931447</v>
+        <v>4.924947031763601</v>
       </c>
       <c r="E29" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F29" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>26.33766427874918</v>
+        <v>4.279870445296742</v>
       </c>
       <c r="D30" t="n">
-        <v>24.35682835229432</v>
+        <v>3.957984607247827</v>
       </c>
       <c r="E30" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F30" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>33.74482603577182</v>
+        <v>5.48353423081292</v>
       </c>
       <c r="D31" t="n">
-        <v>31.88404661725066</v>
+        <v>5.181157575303232</v>
       </c>
       <c r="E31" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F31" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>5.668467100934469</v>
+        <v>0.9211259039018513</v>
       </c>
       <c r="D32" t="n">
-        <v>7.603538914386855</v>
+        <v>1.235575073587864</v>
       </c>
       <c r="E32" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F32" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>7.360861816987208</v>
+        <v>1.196140045260421</v>
       </c>
       <c r="D33" t="n">
-        <v>8.047463844845897</v>
+        <v>1.307712874787458</v>
       </c>
       <c r="E33" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F33" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>7.957108408382584</v>
+        <v>1.29303011636217</v>
       </c>
       <c r="D34" t="n">
-        <v>10.39510802817664</v>
+        <v>1.689205054578704</v>
       </c>
       <c r="E34" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F34" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>40.2248701459087</v>
+        <v>6.536541398710163</v>
       </c>
       <c r="D35" t="n">
-        <v>33.71940623415915</v>
+        <v>5.479403513050863</v>
       </c>
       <c r="E35" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F35" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>14.02543901468098</v>
+        <v>2.279133839885659</v>
       </c>
       <c r="D36" t="n">
-        <v>8.91406879596688</v>
+        <v>1.448536179344618</v>
       </c>
       <c r="E36" t="n">
-        <v>23.61464925271661</v>
+        <v>3.837380503566449</v>
       </c>
       <c r="F36" t="n">
-        <v>24.29692126007306</v>
+        <v>3.948249704761872</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
